--- a/tabular/genus/boca-refseqs-side-data.xlsx
+++ b/tabular/genus/boca-refseqs-side-data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10308"/>
   <workbookPr date1904="1" showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/robertgifford/Projects/virus/comparative/DNA/Parvovirus-GLUE/tabular/genus/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/diversity/Parvovirus-GLUE/tabular/genus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01210732-9B2E-DA45-BD6A-2D3572D80061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BE1E96A-58BD-5048-AC73-54F6DB00EAF6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21140" yWindow="5400" windowWidth="28800" windowHeight="17540" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="880" yWindow="500" windowWidth="27920" windowHeight="17500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="REFSET" sheetId="3" r:id="rId1"/>
@@ -2185,7 +2185,32 @@
     <cellStyle name="Hyperlink" xfId="913" builtinId="8" hidden="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF660066"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <colors>
     <mruColors>
@@ -2203,6 +2228,27 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{65F3F894-58D3-4E47-8AA4-01A9C42874EC}" name="Table1" displayName="Table1" ref="A1:L18" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:L18" xr:uid="{AFD47828-E405-0B47-BD05-F753F6991222}"/>
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{A8E057E4-8709-084F-A2E5-7196D779FE02}" name="sequenceID"/>
+    <tableColumn id="2" xr3:uid="{391D4813-D497-EA40-9FA3-E95460BFD375}" name="virus_name"/>
+    <tableColumn id="3" xr3:uid="{06909268-2EEC-3A43-8715-81400B138DE5}" name="virus_full_name"/>
+    <tableColumn id="4" xr3:uid="{96BA4C3E-6198-7F45-A18D-1D48C463DC49}" name="host_species"/>
+    <tableColumn id="5" xr3:uid="{6E4CB485-1FA4-7447-86E0-3B64A6E8064E}" name="assign_clade"/>
+    <tableColumn id="6" xr3:uid="{624585C9-993D-AA43-81BF-C4171BB67693}" name="virus_subfamily"/>
+    <tableColumn id="7" xr3:uid="{4B79861C-F34D-BA42-AAC1-33245350B60C}" name="virus_genus"/>
+    <tableColumn id="8" xr3:uid="{B9AA910C-4E93-E443-8673-B70A4642E658}" name="assign_subclade"/>
+    <tableColumn id="9" xr3:uid="{38BC1621-7250-0845-B694-131216FAF04C}" name="virus_clade_ns"/>
+    <tableColumn id="10" xr3:uid="{FBAADA38-9A48-E442-818E-6D476A32E2BC}" name="virus_subclade_ns"/>
+    <tableColumn id="11" xr3:uid="{3C47C91D-3ACC-E949-AF0D-0C98E717FCB8}" name="virus_clade_vp"/>
+    <tableColumn id="12" xr3:uid="{C4606A88-7180-124F-8855-2AAF8DE0BD22}" name="virus_subclade_vp"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2534,11 +2580,12 @@
     <col min="2" max="2" width="17.33203125" customWidth="1"/>
     <col min="3" max="3" width="41" customWidth="1"/>
     <col min="4" max="4" width="26.33203125" customWidth="1"/>
-    <col min="5" max="6" width="15.1640625" customWidth="1"/>
+    <col min="5" max="5" width="15.1640625" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" customWidth="1"/>
     <col min="7" max="8" width="18.6640625" customWidth="1"/>
     <col min="9" max="9" width="16" customWidth="1"/>
     <col min="10" max="10" width="18.5" customWidth="1"/>
-    <col min="11" max="11" width="15.5" customWidth="1"/>
+    <col min="11" max="11" width="15.83203125" customWidth="1"/>
     <col min="12" max="12" width="19.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3232,6 +3279,9 @@
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
   <extLst>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
       <mx:PLV Mode="0" OnePage="0" WScale="0"/>
